--- a/results/Stage3Candidates.xlsx
+++ b/results/Stage3Candidates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhhm1\Documents\ML_Discovery_Metal-Organic_Adsorbents\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745B6B53-46B3-4963-A283-D3E09F091EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A726ABF-2F56-4FBB-95DF-7EE8C3612EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="432" yWindow="576" windowWidth="19176" windowHeight="11148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -619,12 +619,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +659,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -694,7 +694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -729,7 +729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -764,7 +764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -799,7 +799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -834,7 +834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -869,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -904,7 +904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -974,7 +974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>16</v>
       </c>
